--- a/plantillas/plantilla_base.xlsx
+++ b/plantillas/plantilla_base.xlsx
@@ -832,64 +832,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>None</author>
-  </authors>
-  <commentList>
-    <comment ref="L5" authorId="0" shapeId="0">
-      <text>
-        <t>======
-ID#AAAB1p2XQA8
-msuarez    (2026-03-11 22:39:39)
-Interno: Se realizará entre las sedes de la Institución.
-Externo: Se realizará hacia un sitio diferente a las sedes de la Institución.</t>
-      </text>
-    </comment>
-    <comment ref="I7" authorId="0" shapeId="0">
-      <text>
-        <t>======
-ID#AAAB1p2XQCI
-msuarez    (2026-03-11 22:39:39)
-Responsable: Es la persona que tiene a su cargo el (los)  Bien (es).
-Solicitante(s):  persona(s) que va(n) a realizar el traslado o utlizar el o los bienes que se trasladan.
-LOS DATOS DEL SOLICITANTE Y DEL RESPONSABLE DEBEN SER DILIGENCIADOS EN SU TOTALIDAD.</t>
-      </text>
-    </comment>
-    <comment ref="I11" authorId="0" shapeId="0">
-      <text>
-        <t>======
-ID#AAAB1p2XQCE
-msuarez    (2026-03-11 22:39:39)
-Dep: Dependencia.
-Emp: Empresa.
-Dir: Dirección.</t>
-      </text>
-    </comment>
-    <comment ref="B15" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Acá van los elementos que van a pedir. EJ: Audifonos Shure SRH440A
-</t>
-      </text>
-    </comment>
-    <comment ref="I15" authorId="0" shapeId="0">
-      <text>
-        <t>Acá va la cantidad en números de dicho elemento</t>
-      </text>
-    </comment>
-    <comment ref="A39" authorId="0" shapeId="0">
-      <text>
-        <t>======
-ID#AAAB1p2XQCA
-hjerez    (2026-03-11 22:39:39)
-Otros Solicitantes: Si requiere registrar más solicitantes inserte el número de filas correspondiente</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2130,6 +2072,5 @@
     <mergeCell ref="P1:P20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>